--- a/data/trans_orig/P1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007</t>
+          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>51116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>39057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>50494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83705</t>
+          <t>83350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>421982</t>
+          <t>422660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>447496</t>
+          <t>447172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266740</t>
+          <t>267623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286625</t>
+          <t>287199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696752</t>
+          <t>697107</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>728094</t>
+          <t>729963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33074</t>
+          <t>33508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>61977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38650</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58106</t>
+          <t>56631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91801</t>
+          <t>91698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>306962</t>
+          <t>304957</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333860</t>
+          <t>333426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333215</t>
+          <t>334695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353339</t>
+          <t>353713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646998</t>
+          <t>647101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680693</t>
+          <t>682168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>21050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>29784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55494</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>498882</t>
+          <t>499134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521521</t>
+          <t>521339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148406</t>
+          <t>149466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161715</t>
+          <t>162199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654677</t>
+          <t>655173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680179</t>
+          <t>680387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66953</t>
+          <t>65460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101498</t>
+          <t>102889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>38917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65970</t>
+          <t>67790</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113354</t>
+          <t>112494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157711</t>
+          <t>157795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1136836</t>
+          <t>1135445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1171381</t>
+          <t>1172874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648315</t>
+          <t>646495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>675279</t>
+          <t>675368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1794909</t>
+          <t>1794825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1839266</t>
+          <t>1840126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48487</t>
+          <t>48460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35736</t>
+          <t>34650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61121</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67007</t>
+          <t>67469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102024</t>
+          <t>103040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302068</t>
+          <t>302095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325093</t>
+          <t>326321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507631</t>
+          <t>505848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533016</t>
+          <t>534102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>817283</t>
+          <t>816267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>852300</t>
+          <t>851838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110370</t>
+          <t>108818</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>154796</t>
+          <t>153903</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>114216</t>
+          <t>115326</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160141</t>
+          <t>162287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284274</t>
+          <t>283298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295477</t>
+          <t>295400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1093964</t>
+          <t>1094857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1138390</t>
+          <t>1139942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1386819</t>
+          <t>1384673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1432744</t>
+          <t>1431634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209937</t>
+          <t>208894</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>270930</t>
+          <t>270457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>266389</t>
+          <t>263915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>331430</t>
+          <t>333247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>491032</t>
+          <t>490279</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>578056</t>
+          <t>579501</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2999260</t>
+          <t>2999733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3060253</t>
+          <t>3061296</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3046694</t>
+          <t>3044877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3111735</t>
+          <t>3114209</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6070258</t>
+          <t>6068813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6157282</t>
+          <t>6158035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012</t>
+          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>36534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63398</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>28736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54663</t>
+          <t>56043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71302</t>
+          <t>73660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>110914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373813</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401004</t>
+          <t>400677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259791</t>
+          <t>258411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285415</t>
+          <t>285718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>642180</t>
+          <t>640751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>680363</t>
+          <t>678005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26178</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52148</t>
+          <t>50461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37323</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48832</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82535</t>
+          <t>79974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366649</t>
+          <t>368336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392619</t>
+          <t>392784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300688</t>
+          <t>300085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321184</t>
+          <t>320827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674273</t>
+          <t>676834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707976</t>
+          <t>709100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36802</t>
+          <t>35563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67593</t>
+          <t>66266</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19755</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>40101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63350</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100683</t>
+          <t>99451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561822</t>
+          <t>563149</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>592613</t>
+          <t>593852</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219173</t>
+          <t>220028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240374</t>
+          <t>239938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>788861</t>
+          <t>790093</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>826194</t>
+          <t>825414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83486</t>
+          <t>82470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>121231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29642</t>
+          <t>28862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56675</t>
+          <t>55966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,47 +4447,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>142316</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>119278</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>164884</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>7,39%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>142316</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>121551</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>167993</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1035441</t>
+          <t>1037778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1075523</t>
+          <t>1076539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>709982</t>
+          <t>710691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737015</t>
+          <t>737795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,47 +4560,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1783351</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1760783</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1806389</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>92,61%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1783351</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1757674</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1804116</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>54149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63222</t>
+          <t>63648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96932</t>
+          <t>98767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99851</t>
+          <t>100639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143045</t>
+          <t>142142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457054</t>
+          <t>456447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>481870</t>
+          <t>481114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>664590</t>
+          <t>662755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>698300</t>
+          <t>697874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129073</t>
+          <t>1129976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1172267</t>
+          <t>1171479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115625</t>
+          <t>115086</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160299</t>
+          <t>160369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122245</t>
+          <t>120804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169231</t>
+          <t>170600</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252473</t>
+          <t>252679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263693</t>
+          <t>263664</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>949052</t>
+          <t>948982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>993726</t>
+          <t>994265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1207002</t>
+          <t>1205633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1253988</t>
+          <t>1255429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>249558</t>
+          <t>251247</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>322603</t>
+          <t>320672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>316939</t>
+          <t>318557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>390171</t>
+          <t>391109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>591893</t>
+          <t>590588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>688869</t>
+          <t>690751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3099307</t>
+          <t>3101238</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3172352</t>
+          <t>3170663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3159954</t>
+          <t>3159016</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3233186</t>
+          <t>3231568</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6283166</t>
+          <t>6281284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6380142</t>
+          <t>6381447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016</t>
+          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75526</t>
+          <t>73531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114566</t>
+          <t>111100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63870</t>
+          <t>64579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120595</t>
+          <t>120931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167227</t>
+          <t>165386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>314526</t>
+          <t>317992</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>353566</t>
+          <t>355561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283185</t>
+          <t>282476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311057</t>
+          <t>311129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608920</t>
+          <t>610761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655552</t>
+          <t>655216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>27636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51985</t>
+          <t>50456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>35076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60939</t>
+          <t>62128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>68013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105258</t>
+          <t>103115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325242</t>
+          <t>326771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349522</t>
+          <t>349591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311334</t>
+          <t>310145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338272</t>
+          <t>337197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>644242</t>
+          <t>646385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680885</t>
+          <t>681487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42553</t>
+          <t>43898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70691</t>
+          <t>72417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66335</t>
+          <t>68256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103407</t>
+          <t>103934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451223</t>
+          <t>449497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479361</t>
+          <t>478016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126554</t>
+          <t>127119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148479</t>
+          <t>147453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584629</t>
+          <t>584102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621701</t>
+          <t>619780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99966</t>
+          <t>101777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142829</t>
+          <t>141597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87320</t>
+          <t>86162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>129607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200837</t>
+          <t>198008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257111</t>
+          <t>256193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1006809</t>
+          <t>1008041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1049672</t>
+          <t>1047861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>698449</t>
+          <t>696269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>738556</t>
+          <t>739714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1718403</t>
+          <t>1719321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1774677</t>
+          <t>1777506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75735</t>
+          <t>74911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112404</t>
+          <t>110627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>67754</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104149</t>
+          <t>103864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154734</t>
+          <t>155692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204416</t>
+          <t>200904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>508302</t>
+          <t>510079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544971</t>
+          <t>545795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634095</t>
+          <t>634380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>670658</t>
+          <t>670490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1154534</t>
+          <t>1158046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1204216</t>
+          <t>1203258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128147</t>
+          <t>127821</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179164</t>
+          <t>175600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>152484</t>
+          <t>147760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205464</t>
+          <t>203872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251563</t>
+          <t>251916</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271057</t>
+          <t>271739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>902861</t>
+          <t>906425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>953878</t>
+          <t>954204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1163706</t>
+          <t>1165298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1216686</t>
+          <t>1221410</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>384169</t>
+          <t>386193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>463953</t>
+          <t>463663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>428406</t>
+          <t>424266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>516185</t>
+          <t>513675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>835690</t>
+          <t>835327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>951913</t>
+          <t>953403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2921769</t>
+          <t>2922059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3001553</t>
+          <t>2999529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3015411</t>
+          <t>3017921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3103190</t>
+          <t>3107330</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5965405</t>
+          <t>5963915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6081628</t>
+          <t>6081991</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023</t>
+          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71299</t>
+          <t>71107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108194</t>
+          <t>107439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62257</t>
+          <t>60966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87664</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141298</t>
+          <t>139628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>184581</t>
+          <t>182677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>397018</t>
+          <t>397773</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433913</t>
+          <t>434105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>359892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>385210</t>
+          <t>386501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>768098</t>
+          <t>770002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811381</t>
+          <t>813051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>68099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101285</t>
+          <t>100638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43373</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65161</t>
+          <t>64945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116739</t>
+          <t>119129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156830</t>
+          <t>157293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350928</t>
+          <t>351575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>382596</t>
+          <t>384114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317419</t>
+          <t>317635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339207</t>
+          <t>338145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677963</t>
+          <t>677500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718054</t>
+          <t>715664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133619</t>
+          <t>133125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27845</t>
+          <t>27436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44368</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48922</t>
+          <t>56380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170875</t>
+          <t>169135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534645</t>
+          <t>535139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639173</t>
+          <t>639614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122543</t>
+          <t>123047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139066</t>
+          <t>139475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664300</t>
+          <t>666040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>786253</t>
+          <t>778795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173430</t>
+          <t>174391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>224375</t>
+          <t>224821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>62987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151670</t>
+          <t>150539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>217435</t>
+          <t>209961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>358331</t>
+          <t>356895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>810444</t>
+          <t>809998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>861389</t>
+          <t>860428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>826424</t>
+          <t>827555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>920563</t>
+          <t>915107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1654581</t>
+          <t>1656017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1795477</t>
+          <t>1802951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90867</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127783</t>
+          <t>128035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117543</t>
+          <t>114293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>182535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215918</t>
+          <t>216463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296220</t>
+          <t>299462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>347263</t>
+          <t>347011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>384179</t>
+          <t>385621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659275</t>
+          <t>658800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>723792</t>
+          <t>727042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1020161</t>
+          <t>1016919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1100463</t>
+          <t>1099918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38262</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>136756</t>
+          <t>139549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>174833</t>
+          <t>176816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147827</t>
+          <t>147078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>193434</t>
+          <t>193958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202245</t>
+          <t>207692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235758</t>
+          <t>235811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>586538</t>
+          <t>584555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>624615</t>
+          <t>621822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>808444</t>
+          <t>807920</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>854051</t>
+          <t>854800</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>442701</t>
+          <t>454229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>633167</t>
+          <t>635500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>482538</t>
+          <t>482380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>643790</t>
+          <t>649175</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1009593</t>
+          <t>1002690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1254433</t>
+          <t>1246614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2742893</t>
+          <t>2740560</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2933359</t>
+          <t>2921831</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2933968</t>
+          <t>2928583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3095220</t>
+          <t>3095378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5699385</t>
+          <t>5707204</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5944225</t>
+          <t>5951128</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51116</t>
+          <t>52049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39057</t>
+          <t>40032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>50721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>83040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422660</t>
+          <t>421727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>447172</t>
+          <t>446409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267623</t>
+          <t>266648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287199</t>
+          <t>286483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697107</t>
+          <t>697417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729963</t>
+          <t>729736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>32767</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61977</t>
+          <t>59217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37170</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56631</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91698</t>
+          <t>92267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304957</t>
+          <t>307717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333426</t>
+          <t>334167</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334695</t>
+          <t>332799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353713</t>
+          <t>352427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647101</t>
+          <t>646532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>682168</t>
+          <t>680892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18316</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54998</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499134</t>
+          <t>498529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521339</t>
+          <t>521638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149466</t>
+          <t>149568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162199</t>
+          <t>162069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655173</t>
+          <t>655112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680387</t>
+          <t>680101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65460</t>
+          <t>65436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102889</t>
+          <t>102701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38917</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67790</t>
+          <t>65605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112494</t>
+          <t>112335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157795</t>
+          <t>157132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1135445</t>
+          <t>1135633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1172874</t>
+          <t>1172898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>646495</t>
+          <t>648680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>675368</t>
+          <t>676270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1794825</t>
+          <t>1795488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1840126</t>
+          <t>1840285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>24525</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>48761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>35282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62904</t>
+          <t>63290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67469</t>
+          <t>66245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103040</t>
+          <t>100342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302095</t>
+          <t>301794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>326321</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>505848</t>
+          <t>505462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534102</t>
+          <t>533470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>816267</t>
+          <t>818965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>851838</t>
+          <t>853062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>108818</t>
+          <t>111444</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>153903</t>
+          <t>156821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115326</t>
+          <t>118019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162287</t>
+          <t>163686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283298</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295400</t>
+          <t>295418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1094857</t>
+          <t>1091939</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1139942</t>
+          <t>1137316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1384673</t>
+          <t>1383274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1431634</t>
+          <t>1428941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208894</t>
+          <t>207856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>270457</t>
+          <t>269765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>263915</t>
+          <t>265543</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>333247</t>
+          <t>329610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>490279</t>
+          <t>495791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>579501</t>
+          <t>587312</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2999733</t>
+          <t>3000425</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3061296</t>
+          <t>3062334</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3044877</t>
+          <t>3048514</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3114209</t>
+          <t>3112581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6068813</t>
+          <t>6061002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6158035</t>
+          <t>6152523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36534</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>64419</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28736</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56043</t>
+          <t>55917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>72161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110914</t>
+          <t>110063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373035</t>
+          <t>372792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400677</t>
+          <t>400396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258411</t>
+          <t>258537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285718</t>
+          <t>285085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>640751</t>
+          <t>641602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>678005</t>
+          <t>679504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26013</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>37396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>49523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79974</t>
+          <t>81617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368336</t>
+          <t>367528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392784</t>
+          <t>392927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300085</t>
+          <t>300615</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320827</t>
+          <t>320487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>676834</t>
+          <t>675191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709100</t>
+          <t>707285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>37176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66266</t>
+          <t>68774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>39622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64130</t>
+          <t>64079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99451</t>
+          <t>99127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>563149</t>
+          <t>560641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>593852</t>
+          <t>592239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220028</t>
+          <t>220507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239938</t>
+          <t>240315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790093</t>
+          <t>790417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825414</t>
+          <t>825465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82470</t>
+          <t>83143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121231</t>
+          <t>124966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28862</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55966</t>
+          <t>56121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119278</t>
+          <t>120285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164884</t>
+          <t>166937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1037778</t>
+          <t>1034043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1076539</t>
+          <t>1075866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>710691</t>
+          <t>710536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737795</t>
+          <t>736606</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1760783</t>
+          <t>1758730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1806389</t>
+          <t>1805382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>29726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>55036</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63648</t>
+          <t>65436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98767</t>
+          <t>99886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100639</t>
+          <t>100144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142142</t>
+          <t>144493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456447</t>
+          <t>455560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>481114</t>
+          <t>480870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662755</t>
+          <t>661636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697874</t>
+          <t>696086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129976</t>
+          <t>1127625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1171479</t>
+          <t>1171974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115086</t>
+          <t>116394</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160369</t>
+          <t>159287</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120804</t>
+          <t>122139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170600</t>
+          <t>169369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252679</t>
+          <t>252675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263664</t>
+          <t>263536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>948982</t>
+          <t>950064</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>994265</t>
+          <t>992957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1205633</t>
+          <t>1206864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1255429</t>
+          <t>1254094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>251247</t>
+          <t>250759</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>320672</t>
+          <t>320468</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>318557</t>
+          <t>315812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>391109</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>590588</t>
+          <t>590917</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>690751</t>
+          <t>697437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3101238</t>
+          <t>3101442</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3170663</t>
+          <t>3171151</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3159016</t>
+          <t>3160125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3231568</t>
+          <t>3234313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6281284</t>
+          <t>6274598</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6381447</t>
+          <t>6381118</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73531</t>
+          <t>74127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111100</t>
+          <t>111409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>37857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64579</t>
+          <t>65423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120931</t>
+          <t>120701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165386</t>
+          <t>167011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>317992</t>
+          <t>317683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355561</t>
+          <t>354965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282476</t>
+          <t>281632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311129</t>
+          <t>309198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>610761</t>
+          <t>609136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655216</t>
+          <t>655446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27636</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>50532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62128</t>
+          <t>62519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68013</t>
+          <t>69146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103115</t>
+          <t>105549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>326771</t>
+          <t>326695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>349591</t>
+          <t>350174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310145</t>
+          <t>309754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337197</t>
+          <t>337675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646385</t>
+          <t>643951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681487</t>
+          <t>680354</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43898</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72417</t>
+          <t>70691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39004</t>
+          <t>38970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>68518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>103635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>449497</t>
+          <t>451223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478016</t>
+          <t>479388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127119</t>
+          <t>127153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147453</t>
+          <t>147805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584102</t>
+          <t>584401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>619780</t>
+          <t>619518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101777</t>
+          <t>100877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141597</t>
+          <t>143580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86162</t>
+          <t>88520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129607</t>
+          <t>128306</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198008</t>
+          <t>198484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256193</t>
+          <t>256389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1008041</t>
+          <t>1006058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1047861</t>
+          <t>1048761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696269</t>
+          <t>697570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>739714</t>
+          <t>737356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1719321</t>
+          <t>1719125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1777506</t>
+          <t>1777030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74911</t>
+          <t>76283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110627</t>
+          <t>112194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67754</t>
+          <t>68029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103864</t>
+          <t>104418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155692</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200904</t>
+          <t>204163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>510079</t>
+          <t>508512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>545795</t>
+          <t>544423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634380</t>
+          <t>633826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>670490</t>
+          <t>670215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1158046</t>
+          <t>1154787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1203258</t>
+          <t>1204663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>34886</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>129674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175600</t>
+          <t>178953</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147760</t>
+          <t>152917</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>203872</t>
+          <t>205629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251916</t>
+          <t>252259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271739</t>
+          <t>271269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>906425</t>
+          <t>903072</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>954204</t>
+          <t>952351</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1165298</t>
+          <t>1163541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1221410</t>
+          <t>1216253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>386193</t>
+          <t>384427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>463663</t>
+          <t>461398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>424266</t>
+          <t>431472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>513675</t>
+          <t>512690</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>835327</t>
+          <t>834154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>953403</t>
+          <t>945728</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2922059</t>
+          <t>2924324</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2999529</t>
+          <t>3001295</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3017921</t>
+          <t>3018906</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3107330</t>
+          <t>3100124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5963915</t>
+          <t>5971590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6081991</t>
+          <t>6083164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87436</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71107</t>
+          <t>77994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107439</t>
+          <t>115780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>83202</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60966</t>
+          <t>70054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>96738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>161689</t>
+          <t>178174</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139628</t>
+          <t>156520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182677</t>
+          <t>203780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>417776</t>
+          <t>455645</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>397773</t>
+          <t>434838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434105</t>
+          <t>472624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>373214</t>
+          <t>405209</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>359892</t>
+          <t>391673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>386501</t>
+          <t>418357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>790990</t>
+          <t>860855</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770002</t>
+          <t>835249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813051</t>
+          <t>882509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>88795</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68099</t>
+          <t>72564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100638</t>
+          <t>107455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>60980</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>49785</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>73931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>137817</t>
+          <t>149775</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119129</t>
+          <t>130798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157293</t>
+          <t>172110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>368406</t>
+          <t>394417</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351575</t>
+          <t>375757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>384114</t>
+          <t>410648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>328570</t>
+          <t>362163</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317635</t>
+          <t>349212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338145</t>
+          <t>373358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>696976</t>
+          <t>756580</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677500</t>
+          <t>734245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715664</t>
+          <t>775557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80180</t>
+          <t>85167</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>69158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133125</t>
+          <t>103277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>38932</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27436</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43864</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115391</t>
+          <t>124099</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56380</t>
+          <t>106710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169135</t>
+          <t>144494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>588084</t>
+          <t>386445</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535139</t>
+          <t>368335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639614</t>
+          <t>402454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>131700</t>
+          <t>148565</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123047</t>
+          <t>139489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139475</t>
+          <t>156873</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>719784</t>
+          <t>535010</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>666040</t>
+          <t>514615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>778795</t>
+          <t>552399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>83,81%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>197587</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>174391</t>
+          <t>191215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>224821</t>
+          <t>248387</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>112952</t>
+          <t>123241</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62987</t>
+          <t>108182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150539</t>
+          <t>142696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>310539</t>
+          <t>343266</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209961</t>
+          <t>312921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>356895</t>
+          <t>380290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>837232</t>
+          <t>911818</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>809998</t>
+          <t>883456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860428</t>
+          <t>940628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>865142</t>
+          <t>737970</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>827555</t>
+          <t>718515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>915107</t>
+          <t>753029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1702373</t>
+          <t>1649788</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1656017</t>
+          <t>1612764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1802951</t>
+          <t>1680133</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>140943</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89425</t>
+          <t>117448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128035</t>
+          <t>162928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>157191</t>
+          <t>168407</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114293</t>
+          <t>151584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182535</t>
+          <t>185868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>265811</t>
+          <t>309350</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216463</t>
+          <t>280198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299462</t>
+          <t>338614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>366427</t>
+          <t>427021</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>347011</t>
+          <t>405036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385621</t>
+          <t>450516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>684144</t>
+          <t>662443</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>658800</t>
+          <t>644982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>727042</t>
+          <t>679266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1050570</t>
+          <t>1089464</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1016919</t>
+          <t>1060200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1099918</t>
+          <t>1118616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>156432</t>
+          <t>169062</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139549</t>
+          <t>151269</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176816</t>
+          <t>189822</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>168397</t>
+          <t>179346</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>147078</t>
+          <t>158594</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>193958</t>
+          <t>201777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>228542</t>
+          <t>226944</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207692</t>
+          <t>215587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235811</t>
+          <t>232701</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>604939</t>
+          <t>675219</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>584555</t>
+          <t>654459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>621822</t>
+          <t>693012</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>833481</t>
+          <t>902163</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>807920</t>
+          <t>879732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>854800</t>
+          <t>922915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>569593</t>
+          <t>640187</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>454229</t>
+          <t>595586</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>635500</t>
+          <t>690721</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,67 +10726,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>590050</t>
+          <t>643823</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>482380</t>
+          <t>603732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>649175</t>
+          <t>680237</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>18,71%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1284010</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1217370</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1340301</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>18,14%</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1159643</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1002690</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1246614</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2806467</t>
+          <t>2802289</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2740560</t>
+          <t>2751755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2921831</t>
+          <t>2846890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,67 +10839,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2987708</t>
+          <t>2991570</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2928583</t>
+          <t>2955156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3095378</t>
+          <t>3031661</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>81,29%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>6763</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>5793859</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>5737568</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>5860499</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>81,86%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>6763</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>5794175</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>5707204</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>5951128</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>83,32%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
